--- a/nr-rm-adeli/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
+++ b/nr-rm-adeli/ig/StructureDefinition-fr-core-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-06T10:53:29+00:00</t>
+    <t>2024-10-29T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profil Body weight based on the FHIR profil BodyWeightMeas.
+    <t>French profile of body weight based on the FHIR profil BodyWeightMeas.
 Profil français Body weight basé sur le profil HL7 BodyWeightMeas de Vital Signs.</t>
   </si>
   <si>
